--- a/outputs/61-4.xlsx
+++ b/outputs/61-4.xlsx
@@ -401,108 +401,112 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -758,824 +762,824 @@
   <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="8.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="5.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="5.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="9.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="53.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="8.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="5.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="53.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45186</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>58.5</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>56.6</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>57.1</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="G2" s="8" t="n">
         <v>554558</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>45186</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="9" t="n">
+      <c r="L2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="10" t="n">
         <v>59.6</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="N2" s="11" t="n">
         <v>59.6</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="O2" s="6" t="n">
         <v>56.6</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="P2" s="7" t="n">
         <v>57.1</v>
       </c>
-      <c r="Q2" s="0" t="n">
+      <c r="Q2" s="1" t="n">
         <v>1521647</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45183</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="n">
         <v>58.4</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>59.5</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>58.1</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>58.3</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>327685</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="9" t="n">
         <v>-0.400000000000006</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45182</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="9" t="n">
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>59.6</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <v>59.6</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>58.7</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>639404</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>45181</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>59.7</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="12" t="n">
         <v>45181</v>
       </c>
-      <c r="L5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" s="0" t="n">
+      <c r="L5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <v>59.7</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="1"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="13" t="n">
         <v>45180</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="13" t="n">
+      <c r="B6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>60.3</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>59.5</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>59.7</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n">
         <v>300877</v>
       </c>
-      <c r="H6" s="15" t="n">
+      <c r="H6" s="16" t="n">
         <v>-0.399999999999999</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="13" t="n">
         <v>45180</v>
       </c>
-      <c r="L6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="9" t="n">
+      <c r="L6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="10" t="n">
         <v>61.9</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="11" t="n">
         <v>61.9</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="O6" s="6" t="n">
         <v>59.5</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="P6" s="7" t="n">
         <v>59.7</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="1" t="n">
         <v>1234283</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="13" t="n">
         <v>45179</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="13" t="n">
+      <c r="B7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="14" t="n">
         <v>61</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>61.4</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>59.9</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>60.1</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n">
         <v>343589</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="16" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="13" t="n">
         <v>45176</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="9" t="n">
+      <c r="B8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>61.9</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>61.9</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>60.7</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>61.1</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n">
         <v>589817</v>
       </c>
-      <c r="H8" s="15" t="n">
+      <c r="H8" s="16" t="n">
         <v>-0.799999999999997</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>45174</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>62.1</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>62.4</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>61.3</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>61.9</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>582049</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.100000000000001</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <v>45174</v>
       </c>
-      <c r="L9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="0" t="n">
+      <c r="L9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>62.1</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>62.4</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>61.3</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9" s="1" t="n">
         <v>61.9</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="17" t="n">
         <v>582049</v>
       </c>
-      <c r="R9" s="1"/>
+      <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="13" t="n">
         <v>45173</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="B10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="14" t="n">
         <v>62.8</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>63.2</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>61.4</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>61.8</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n">
         <v>478620</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="16" t="n">
         <v>-0.800000000000004</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="13" t="n">
         <v>45173</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="13" t="n">
+      <c r="L10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="14" t="n">
         <v>62.8</v>
       </c>
-      <c r="N10" s="13" t="n">
+      <c r="N10" s="14" t="n">
         <v>63.2</v>
       </c>
-      <c r="O10" s="13" t="n">
+      <c r="O10" s="14" t="n">
         <v>61.4</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="14" t="n">
         <v>61.8</v>
       </c>
-      <c r="Q10" s="14" t="n">
+      <c r="Q10" s="15" t="n">
         <v>478620</v>
       </c>
-      <c r="R10" s="15"/>
+      <c r="R10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>45172</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>62.6</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>61.8</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>62.6</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>660444</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.600000000000001</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="12" t="n">
         <v>45172</v>
       </c>
-      <c r="L11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="0" t="n">
+      <c r="L11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>62.6</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>61.8</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11" s="1" t="n">
         <v>62.6</v>
       </c>
-      <c r="Q11" s="16" t="n">
+      <c r="Q11" s="17" t="n">
         <v>660444</v>
       </c>
-      <c r="R11" s="1"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <v>45186</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>22.7</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>1116072</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.699999999999999</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="12" t="n">
         <v>45186</v>
       </c>
-      <c r="L12" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="M12" s="0" t="n">
+      <c r="L12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="1" t="n">
         <v>22.7</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="17" t="n">
         <v>1116072</v>
       </c>
-      <c r="R12" s="1"/>
+      <c r="R12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="13" t="n">
         <v>45183</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="13" t="n">
+      <c r="B13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>22.8</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>22.8</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="15" t="n">
         <v>608103</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="16" t="n">
         <v>-0.199999999999999</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K13" s="13" t="n">
         <v>45183</v>
       </c>
-      <c r="L13" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="M13" s="9" t="n">
+      <c r="L13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="N13" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="O13" s="6" t="n">
         <v>22.8</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n">
         <v>22.8</v>
       </c>
-      <c r="Q13" s="16" t="n">
+      <c r="Q13" s="17" t="n">
         <v>1254582</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="13" t="n">
         <v>45182</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="9" t="n">
+      <c r="B14" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="15" t="n">
         <v>646479</v>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H14" s="16" t="n">
         <v>-0.199999999999999</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="12" t="n">
         <v>45181</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="0" t="n">
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>23.3</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>23.2</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="17" t="n">
         <v>393986</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.300000000000001</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <v>45181</v>
       </c>
-      <c r="L15" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="M15" s="0" t="n">
+      <c r="L15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <v>23.3</v>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O15" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15" s="1" t="n">
         <v>23.2</v>
       </c>
-      <c r="Q15" s="16" t="n">
+      <c r="Q15" s="17" t="n">
         <v>393986</v>
       </c>
-      <c r="R15" s="1"/>
+      <c r="R15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="18" t="n">
         <v>45180</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="18" t="n">
+      <c r="B16" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <v>23.2</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>23.4</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>22.9</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="21" t="n">
         <v>22.9</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>781927</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="23" t="n">
         <v>-0.300000000000001</v>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="K16" s="18" t="n">
         <v>45180</v>
       </c>
-      <c r="L16" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="M16" s="23" t="n">
+      <c r="L16" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16" s="24" t="n">
         <v>24.2</v>
       </c>
-      <c r="N16" s="24" t="n">
+      <c r="N16" s="25" t="n">
         <v>24.3</v>
       </c>
-      <c r="O16" s="19" t="n">
+      <c r="O16" s="20" t="n">
         <v>22.9</v>
       </c>
-      <c r="P16" s="20" t="n">
+      <c r="P16" s="21" t="n">
         <v>22.9</v>
       </c>
-      <c r="Q16" s="18" t="n">
+      <c r="Q16" s="19" t="n">
         <v>4577093</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="18" t="n">
         <v>45179</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="18" t="n">
+      <c r="B17" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="19" t="n">
         <v>23.5</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>23.8</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="19" t="n">
         <v>23.2</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="22" t="n">
         <v>724897</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="23" t="n">
         <v>-0.300000000000001</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="18" t="n">
         <v>45176</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="18" t="n">
+      <c r="B18" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <v>24.1</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="19" t="n">
         <v>23.4</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="19" t="n">
         <v>23.5</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="22" t="n">
         <v>1022957</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="23" t="n">
         <v>-0.399999999999999</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="18" t="n">
         <v>45174</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="18" t="n">
+      <c r="B19" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="19" t="n">
         <v>24.2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="19" t="n">
         <v>23.8</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="19" t="n">
         <v>23.9</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="22" t="n">
         <v>1347849</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="23" t="n">
         <v>-0.100000000000001</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="n">
+      <c r="A20" s="18" t="n">
         <v>45173</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="23" t="n">
+      <c r="B20" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="24" t="n">
         <v>24.2</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <v>24.3</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="19" t="n">
         <v>23.9</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="22" t="n">
         <v>699463</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="23" t="n">
         <v>-0.199999999999999</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="12" t="n">
         <v>45172</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="0" t="n">
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>24.6</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="F21" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="17" t="n">
         <v>2331697</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <v>0.0999999999999979</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <v>45172</v>
       </c>
-      <c r="L21" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="M21" s="0" t="n">
+      <c r="L21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M21" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <v>24.6</v>
       </c>
-      <c r="O21" s="0" t="n">
+      <c r="O21" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="Q21" s="16" t="n">
+      <c r="Q21" s="17" t="n">
         <v>2331697</v>
       </c>
-      <c r="R21" s="1"/>
+      <c r="R21" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1597,288 +1601,288 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="5.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="59.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="59.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45186</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="9" t="n">
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10" t="n">
         <v>59.6</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="n">
         <v>59.6</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>56.6</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>57.1</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>1521647</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="12" t="n">
         <v>45181</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>59.7</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="13" t="n">
         <v>45180</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="9" t="n">
+      <c r="B4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>61.9</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <v>61.9</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>59.5</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>59.7</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>1234283</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>45174</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>62.1</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>62.4</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>61.3</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>61.9</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <v>582049</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="13" t="n">
         <v>45173</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="13" t="n">
+      <c r="B6" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="14" t="n">
         <v>62.8</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>63.2</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>61.4</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>61.8</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n">
         <v>478620</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="26" t="n">
         <v>45172</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>62.6</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>61.8</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>62.6</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>660444</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="26" t="n">
         <v>45186</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>22.7</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>23.5</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>1116072</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="26" t="n">
         <v>45183</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>23.2</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>23.3</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>22.8</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>1254582</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="26" t="n">
         <v>45181</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>23.3</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>23.2</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>393986</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="26" t="n">
         <v>45180</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>24.3</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="F11" s="0" t="n">
+      <c r="F11" s="1" t="n">
         <v>22.9</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>4577093</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="26" t="n">
         <v>45172</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>24.6</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>24.2</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>2331697</v>
       </c>
     </row>

--- a/outputs/61-4.xlsx
+++ b/outputs/61-4.xlsx
@@ -231,7 +231,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="10">
   <si>
     <t xml:space="preserve">DATE </t>
   </si>
@@ -267,11 +267,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -401,7 +400,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -503,10 +502,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1598,7 +1593,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.75"/>
@@ -1650,79 +1645,79 @@
         <v>56.6</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>57.1</v>
+        <v>58.3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1521647</v>
+        <v>1849332</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="n">
-        <v>45181</v>
+        <v>45180</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59.7</v>
+        <v>61.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0</v>
+        <v>1234283</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="n">
-        <v>45180</v>
+        <v>45183</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>61.9</v>
+        <v>23.2</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>61.9</v>
+        <v>23.3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>59.5</v>
+        <v>22.8</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>59.7</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>1234283</v>
+        <v>1254582</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="n">
-        <v>45174</v>
+        <v>45180</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>62.1</v>
+        <v>24.2</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>62.4</v>
+        <v>24.3</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>61.3</v>
+        <v>22.9</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>61.9</v>
+        <v>24</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>582049</v>
+        <v>4577093</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1746,144 +1741,6 @@
       </c>
       <c r="G6" s="15" t="n">
         <v>478620</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="n">
-        <v>45172</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>660444</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="n">
-        <v>45186</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>1116072</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="n">
-        <v>45183</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1254582</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="n">
-        <v>45181</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>393986</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="n">
-        <v>45180</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>4577093</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="n">
-        <v>45172</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>2331697</v>
       </c>
     </row>
   </sheetData>
